--- a/data.mn/public/datasets/household-income-total.xlsx
+++ b/data.mn/public/datasets/household-income-total.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,351 +434,235 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>56218</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B2" t="n">
+        <v>56218</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>66492</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B3" t="n">
+        <v>66492</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>67426</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B4" t="n">
+        <v>67426</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>108011</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108011</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>111119</t>
-        </is>
+      <c r="A6" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111119</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>156159</t>
-        </is>
+      <c r="A7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B7" t="n">
+        <v>156159</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>178866</t>
-        </is>
+      <c r="A8" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B8" t="n">
+        <v>178866</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>185989</t>
-        </is>
+      <c r="A9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B9" t="n">
+        <v>185989</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>172421</t>
-        </is>
+      <c r="A10" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B10" t="n">
+        <v>172421</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>200179</t>
-        </is>
+      <c r="A11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B11" t="n">
+        <v>200179</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>263681</t>
-        </is>
+      <c r="A12" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B12" t="n">
+        <v>263681</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>363594</t>
-        </is>
+      <c r="A13" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B13" t="n">
+        <v>363594</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>402525</t>
-        </is>
+      <c r="A14" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B14" t="n">
+        <v>402525</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>448027</t>
-        </is>
+      <c r="A15" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B15" t="n">
+        <v>448027</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>573541</t>
-        </is>
+      <c r="A16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B16" t="n">
+        <v>573541</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>819996</t>
-        </is>
+      <c r="A17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B17" t="n">
+        <v>819996</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>959247</t>
-        </is>
+      <c r="A18" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B18" t="n">
+        <v>959247</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1080145</t>
-        </is>
+      <c r="A19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1080145</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1047255</t>
-        </is>
+      <c r="A20" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1047255</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>944153</t>
-        </is>
+      <c r="A21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B21" t="n">
+        <v>944153</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1035506</t>
-        </is>
+      <c r="A22" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1035506</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1181067</t>
-        </is>
+      <c r="A23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1181067</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1343428</t>
-        </is>
+      <c r="A24" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1343428</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1508837</t>
-        </is>
+      <c r="A25" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1508837</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1621454</t>
-        </is>
+      <c r="A26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1621454</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1860584</t>
-        </is>
+      <c r="A27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1860584</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2162342</t>
-        </is>
+      <c r="A28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2162342</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2572619</t>
-        </is>
+      <c r="A29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2572619</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3046637</t>
-        </is>
+      <c r="A30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3046637</v>
       </c>
     </row>
   </sheetData>
@@ -812,351 +696,235 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>56218</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B2" t="n">
+        <v>56218</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>66492</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B3" t="n">
+        <v>66492</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>67426</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B4" t="n">
+        <v>67426</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>108011</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108011</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>111119</t>
-        </is>
+      <c r="A6" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111119</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>156159</t>
-        </is>
+      <c r="A7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B7" t="n">
+        <v>156159</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>178866</t>
-        </is>
+      <c r="A8" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B8" t="n">
+        <v>178866</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>185989</t>
-        </is>
+      <c r="A9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B9" t="n">
+        <v>185989</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>172421</t>
-        </is>
+      <c r="A10" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B10" t="n">
+        <v>172421</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>200179</t>
-        </is>
+      <c r="A11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B11" t="n">
+        <v>200179</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>263681</t>
-        </is>
+      <c r="A12" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B12" t="n">
+        <v>263681</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>363594</t>
-        </is>
+      <c r="A13" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B13" t="n">
+        <v>363594</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>402525</t>
-        </is>
+      <c r="A14" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B14" t="n">
+        <v>402525</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>448027</t>
-        </is>
+      <c r="A15" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B15" t="n">
+        <v>448027</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>573541</t>
-        </is>
+      <c r="A16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B16" t="n">
+        <v>573541</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>819996</t>
-        </is>
+      <c r="A17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B17" t="n">
+        <v>819996</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>959247</t>
-        </is>
+      <c r="A18" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B18" t="n">
+        <v>959247</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1080145</t>
-        </is>
+      <c r="A19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1080145</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1047255</t>
-        </is>
+      <c r="A20" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1047255</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>944153</t>
-        </is>
+      <c r="A21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B21" t="n">
+        <v>944153</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1035506</t>
-        </is>
+      <c r="A22" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1035506</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1181067</t>
-        </is>
+      <c r="A23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1181067</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1343428</t>
-        </is>
+      <c r="A24" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1343428</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1508837</t>
-        </is>
+      <c r="A25" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1508837</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1621454</t>
-        </is>
+      <c r="A26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1621454</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1860584</t>
-        </is>
+      <c r="A27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1860584</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2162342</t>
-        </is>
+      <c r="A28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2162342</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2572619</t>
-        </is>
+      <c r="A29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2572619</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3046637</t>
-        </is>
+      <c r="A30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3046637</v>
       </c>
     </row>
   </sheetData>
